--- a/process_mining_assignment/Input.xlsx
+++ b/process_mining_assignment/Input.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Youssef Maged\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Youssef Maged\Desktop\Business Process Modeling Project\process_mining_assignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EBCDE24-3F3B-4AD3-A480-D8995638924B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA6D73B-0C1E-4434-8DBC-4713708378EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{86A91640-9300-41FE-9A50-DFCE41FB0026}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="65">
   <si>
     <t>Resource</t>
   </si>
@@ -74,9 +74,6 @@
     <t>SYS2</t>
   </si>
   <si>
-    <t>em-6555555556-1</t>
-  </si>
-  <si>
     <t>Emit invoice</t>
   </si>
   <si>
@@ -146,24 +143,12 @@
     <t>Re-3611111111-2</t>
   </si>
   <si>
-    <t>Chu-4208333333-3</t>
-  </si>
-  <si>
     <t>Ch-4243055556-3</t>
   </si>
   <si>
     <t>Ma-6694444444-3</t>
   </si>
   <si>
-    <t>co-6751157407-3</t>
-  </si>
-  <si>
-    <t>Confirm Order</t>
-  </si>
-  <si>
-    <t>Ern-6895833333-3</t>
-  </si>
-  <si>
     <t>Sh-7013888889-3</t>
   </si>
   <si>
@@ -176,9 +161,6 @@
     <t>Re-4305555556-3</t>
   </si>
   <si>
-    <t>AE-4340277778-3</t>
-  </si>
-  <si>
     <t>Ch-3409722222-4</t>
   </si>
   <si>
@@ -203,15 +185,9 @@
     <t>Sh-5715277778-4</t>
   </si>
   <si>
-    <t>Re-5888888889-4</t>
-  </si>
-  <si>
     <t>Event ID</t>
   </si>
   <si>
-    <t xml:space="preserve">case ID </t>
-  </si>
-  <si>
     <t>Timestamp</t>
   </si>
   <si>
@@ -233,128 +209,47 @@
     <t>SYS1</t>
   </si>
   <si>
-    <t>2012-07-30 11:14</t>
-  </si>
-  <si>
-    <t>2012-07-30 14:20</t>
-  </si>
-  <si>
-    <t>2012-07-30 15:10</t>
-  </si>
-  <si>
-    <t>2012-07-30 15:22</t>
-  </si>
-  <si>
-    <t>2012-07-30 15:44</t>
-  </si>
-  <si>
-    <t>2012-08-04 10:02</t>
-  </si>
-  <si>
-    <t>2012-08-05 11:11</t>
-  </si>
-  <si>
-    <t>2012-08-06 09:12</t>
-  </si>
-  <si>
-    <t>2012-08-01 09:44</t>
-  </si>
-  <si>
-    <t>2012-08-01 10:06</t>
-  </si>
-  <si>
-    <t>2012-08-01 11:12</t>
-  </si>
-  <si>
-    <t>2012-08-03 07:50</t>
-  </si>
-  <si>
-    <t>2012-08-04 14:43</t>
-  </si>
-  <si>
-    <t>2012-08-04 14:51</t>
-  </si>
-  <si>
-    <t>2012-08-04 15:20</t>
-  </si>
-  <si>
-    <t>2012-08-04 15:27</t>
-  </si>
-  <si>
-    <t>2012-08-04 17:28</t>
-  </si>
-  <si>
-    <t>2012-08-07 08:40</t>
-  </si>
-  <si>
-    <t>2012-08-07 08:50</t>
-  </si>
-  <si>
-    <t>2012-08-02 10:06</t>
-  </si>
-  <si>
-    <t>2012-08-02 10:11</t>
-  </si>
-  <si>
-    <t>2012-08-02 16:04</t>
-  </si>
-  <si>
-    <t>2012-08-02 16:12</t>
-  </si>
-  <si>
-    <t>2012-08-02 16:33</t>
-  </si>
-  <si>
-    <t>2012-08-02 16:50</t>
-  </si>
-  <si>
-    <t>2012-08-02 16:58</t>
-  </si>
-  <si>
-    <t>2012-08-06 10:20</t>
-  </si>
-  <si>
-    <t>2012-08-06 10:25</t>
-  </si>
-  <si>
-    <t>2012-08-04 08:11</t>
-  </si>
-  <si>
-    <t>2012-08-04 12:00</t>
-  </si>
-  <si>
-    <t>2012-08-04 12:06</t>
-  </si>
-  <si>
-    <t>2012-08-04 12:20</t>
-  </si>
-  <si>
-    <t>2012-08-04 12:32</t>
-  </si>
-  <si>
-    <t>2012-08-08 09:41</t>
-  </si>
-  <si>
-    <t>2012-08-08 13:43</t>
-  </si>
-  <si>
-    <t>2012-08-08 14:08</t>
-  </si>
-  <si>
     <t>Request raw materials</t>
   </si>
   <si>
     <t>Obtain raw materials</t>
+  </si>
+  <si>
+    <t>Em-6555555556-1</t>
+  </si>
+  <si>
+    <t>Ch-4208333333-3</t>
+  </si>
+  <si>
+    <t>Co-6751157407-3</t>
+  </si>
+  <si>
+    <t>Em-6895833333-3</t>
+  </si>
+  <si>
+    <t>Ar-5888888889-4</t>
+  </si>
+  <si>
+    <t>Ar-4340277778-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case ID </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -380,8 +275,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -719,25 +615,25 @@
   <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.21875" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" customWidth="1"/>
-    <col min="4" max="4" width="29.88671875" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -750,14 +646,14 @@
       <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>64</v>
+      <c r="C2" s="1">
+        <v>41120.468055555553</v>
       </c>
       <c r="D2" t="s">
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -767,8 +663,8 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
-        <v>65</v>
+      <c r="C3" s="1">
+        <v>41120.597222222219</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -782,10 +678,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
+        <v>51</v>
+      </c>
+      <c r="C4" s="1">
+        <v>41120.631944444445</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -801,8 +697,8 @@
       <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
-        <v>67</v>
+      <c r="C5" s="1">
+        <v>41120.640277777777</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
@@ -816,13 +712,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="1">
+        <v>41120.655555555553</v>
+      </c>
+      <c r="D6" t="s">
         <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -833,13 +729,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1">
+        <v>41125.418055555558</v>
+      </c>
+      <c r="D7" t="s">
         <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -850,16 +746,16 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="1">
+        <v>41126.46597222222</v>
+      </c>
+      <c r="D8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -867,16 +763,16 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1">
+        <v>41127.383333333331</v>
+      </c>
+      <c r="D9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>19</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -884,16 +780,16 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
+        <v>20</v>
+      </c>
+      <c r="C10" s="1">
+        <v>41122.405555555553</v>
       </c>
       <c r="D10" t="s">
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -901,16 +797,16 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1">
+        <v>41122.42083333333</v>
+      </c>
+      <c r="D11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -918,16 +814,16 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1">
+        <v>41122.466666666667</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
         <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -935,16 +831,16 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1">
+        <v>41124.326388888891</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
         <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -952,16 +848,16 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1">
+        <v>41125.613194444442</v>
+      </c>
+      <c r="D14" t="s">
         <v>28</v>
       </c>
-      <c r="C14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" t="s">
-        <v>29</v>
-      </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -969,16 +865,16 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
+        <v>54</v>
+      </c>
+      <c r="C15" s="1">
+        <v>41125.618750000001</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -986,13 +882,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>78</v>
+        <v>30</v>
+      </c>
+      <c r="C16" s="1">
+        <v>41125.638888888891</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -1003,10 +899,10 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
+        <v>53</v>
+      </c>
+      <c r="C17" s="1">
+        <v>41125.643750000003</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
@@ -1020,16 +916,16 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="1">
+        <v>41125.727777777778</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
         <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1037,13 +933,13 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" t="s">
-        <v>81</v>
+        <v>33</v>
+      </c>
+      <c r="C19" s="1">
+        <v>41128.361111111109</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -1054,16 +950,16 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" t="s">
-        <v>82</v>
+        <v>52</v>
+      </c>
+      <c r="C20" s="1">
+        <v>41128.368055555555</v>
       </c>
       <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
         <v>19</v>
-      </c>
-      <c r="E20" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1071,16 +967,16 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" t="s">
-        <v>83</v>
+        <v>59</v>
+      </c>
+      <c r="C21" s="1">
+        <v>41123.42083333333</v>
       </c>
       <c r="D21" t="s">
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1088,16 +984,16 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
+        <v>34</v>
+      </c>
+      <c r="C22" s="1">
+        <v>41123.424305555556</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E22" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1105,16 +1001,16 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
+        <v>35</v>
+      </c>
+      <c r="C23" s="1">
+        <v>41123.669444444444</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1122,13 +1018,13 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" t="s">
-        <v>86</v>
+        <v>60</v>
+      </c>
+      <c r="C24" s="1">
+        <v>41123.675000000003</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -1139,13 +1035,13 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" t="s">
-        <v>87</v>
+        <v>61</v>
+      </c>
+      <c r="C25" s="1">
+        <v>41123.689583333333</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -1156,10 +1052,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" t="s">
-        <v>88</v>
+        <v>36</v>
+      </c>
+      <c r="C26" s="1">
+        <v>41123.701388888891</v>
       </c>
       <c r="D26" t="s">
         <v>9</v>
@@ -1173,16 +1069,16 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" t="s">
-        <v>89</v>
+        <v>37</v>
+      </c>
+      <c r="C27" s="1">
+        <v>41123.706944444442</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1190,13 +1086,13 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" t="s">
-        <v>90</v>
+        <v>39</v>
+      </c>
+      <c r="C28" s="1">
+        <v>41127.430555555555</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -1207,16 +1103,16 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
+        <v>63</v>
+      </c>
+      <c r="C29" s="1">
+        <v>41127.434027777781</v>
       </c>
       <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
         <v>19</v>
-      </c>
-      <c r="E29" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1224,16 +1120,16 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" t="s">
-        <v>92</v>
+        <v>40</v>
+      </c>
+      <c r="C30" s="1">
+        <v>41125.34097222222</v>
       </c>
       <c r="D30" t="s">
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1241,16 +1137,16 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" t="s">
-        <v>93</v>
+        <v>41</v>
+      </c>
+      <c r="C31" s="1">
+        <v>41125.5</v>
       </c>
       <c r="D31" t="s">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1258,16 +1154,16 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" t="s">
-        <v>94</v>
+        <v>42</v>
+      </c>
+      <c r="C32" s="1">
+        <v>41125.504166666666</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1275,10 +1171,10 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" t="s">
-        <v>95</v>
+        <v>44</v>
+      </c>
+      <c r="C33" s="1">
+        <v>41125.522222222222</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
@@ -1292,13 +1188,13 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" t="s">
-        <v>96</v>
+        <v>45</v>
+      </c>
+      <c r="C34" s="1">
+        <v>41129.40347222222</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -1309,13 +1205,13 @@
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" t="s">
-        <v>97</v>
+        <v>46</v>
+      </c>
+      <c r="C35" s="1">
+        <v>41129.418055555558</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -1326,16 +1222,16 @@
         <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" t="s">
-        <v>98</v>
+        <v>47</v>
+      </c>
+      <c r="C36" s="1">
+        <v>41129.571527777778</v>
       </c>
       <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
         <v>16</v>
-      </c>
-      <c r="E36" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1343,19 +1239,20 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" t="s">
-        <v>99</v>
+        <v>62</v>
+      </c>
+      <c r="C37" s="1">
+        <v>41129.588888888888</v>
       </c>
       <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
         <v>19</v>
       </c>
-      <c r="E37" t="s">
-        <v>20</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>